--- a/static/data/osworld_verified_results.xlsx
+++ b/static/data/osworld_verified_results.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="13260"/>
+    <workbookView windowWidth="27660" windowHeight="13280"/>
   </bookViews>
   <sheets>
     <sheet name="Eval Results" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2518" uniqueCount="778">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2537" uniqueCount="792">
   <si>
     <t>Model</t>
   </si>
@@ -2361,6 +2361,48 @@
   </si>
   <si>
     <t>13.84/17</t>
+  </si>
+  <si>
+    <t>GUI-Owl-1.5 32B</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2602.16855</t>
+  </si>
+  <si>
+    <t>Mobile-Agent Team</t>
+  </si>
+  <si>
+    <t>197.37/356</t>
+  </si>
+  <si>
+    <t>29.96/45</t>
+  </si>
+  <si>
+    <t>20.0/26</t>
+  </si>
+  <si>
+    <t>23.0/47</t>
+  </si>
+  <si>
+    <t>29.99/47</t>
+  </si>
+  <si>
+    <t>14.0/23</t>
+  </si>
+  <si>
+    <t>25.43/93</t>
+  </si>
+  <si>
+    <t>16.0/21</t>
+  </si>
+  <si>
+    <t>13.0/15</t>
+  </si>
+  <si>
+    <t>5.99/16</t>
+  </si>
+  <si>
+    <t>20.0/23</t>
   </si>
 </sst>
 </file>
@@ -13602,29 +13644,73 @@
       <c r="AB135" s="4"/>
       <c r="AC135" s="4"/>
     </row>
-    <row r="136" ht="15.15" spans="1:29">
-      <c r="A136" s="4"/>
-      <c r="B136" s="4"/>
-      <c r="C136" s="4"/>
-      <c r="D136" s="4"/>
-      <c r="E136" s="4"/>
-      <c r="F136" s="4"/>
-      <c r="G136" s="4"/>
-      <c r="H136" s="4"/>
-      <c r="I136" s="4"/>
-      <c r="J136" s="4"/>
-      <c r="K136" s="4"/>
-      <c r="L136" s="4"/>
-      <c r="M136" s="4"/>
-      <c r="N136" s="4"/>
-      <c r="O136" s="4"/>
-      <c r="P136" s="4"/>
-      <c r="Q136" s="4"/>
-      <c r="R136" s="4"/>
-      <c r="S136" s="4"/>
-      <c r="T136" s="4"/>
-      <c r="U136" s="4"/>
-      <c r="V136" s="4"/>
+    <row r="136" ht="29.75" spans="1:29">
+      <c r="A136" s="3" t="s">
+        <v>778</v>
+      </c>
+      <c r="B136" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>779</v>
+      </c>
+      <c r="D136" s="3" t="s">
+        <v>780</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F136" s="7">
+        <v>50</v>
+      </c>
+      <c r="G136" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H136" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I136" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J136" s="14">
+        <v>46108</v>
+      </c>
+      <c r="K136" s="7">
+        <v>55.44</v>
+      </c>
+      <c r="L136" s="3" t="s">
+        <v>781</v>
+      </c>
+      <c r="M136" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="N136" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="O136" s="3" t="s">
+        <v>784</v>
+      </c>
+      <c r="P136" s="3" t="s">
+        <v>785</v>
+      </c>
+      <c r="Q136" s="3" t="s">
+        <v>786</v>
+      </c>
+      <c r="R136" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="S136" s="3" t="s">
+        <v>788</v>
+      </c>
+      <c r="T136" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="U136" s="3" t="s">
+        <v>790</v>
+      </c>
+      <c r="V136" s="3" t="s">
+        <v>791</v>
+      </c>
       <c r="W136" s="4"/>
       <c r="X136" s="4"/>
       <c r="Y136" s="4"/>
@@ -42932,6 +43018,7 @@
     <hyperlink ref="C133" r:id="rId37" display="https://github.com/MoonshotAI/Kimi-K2.5/blob/master/tech_report.pdf" tooltip="https://github.com/MoonshotAI/Kimi-K2.5/blob/master/tech_report.pdf"/>
     <hyperlink ref="C134" r:id="rId38" display="https://github.com/wadang/muscle-mem-agent" tooltip="https://github.com/wadang/muscle-mem-agent"/>
     <hyperlink ref="C135" r:id="rId39" display="https://www.anthropic.com/news/claude-sonnet-4-6" tooltip="https://www.anthropic.com/news/claude-sonnet-4-6"/>
+    <hyperlink ref="C136" r:id="rId40" display="https://arxiv.org/abs/2602.16855" tooltip="https://arxiv.org/abs/2602.16855"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/static/data/osworld_verified_results.xlsx
+++ b/static/data/osworld_verified_results.xlsx
@@ -12307,8 +12307,8 @@
       <c r="D118" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E118" s="10" t="s">
-        <v>74</v>
+      <c r="E118" s="6" t="s">
+        <v>26</v>
       </c>
       <c r="F118" s="7">
         <v>100</v>

--- a/static/data/osworld_verified_results.xlsx
+++ b/static/data/osworld_verified_results.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="13280"/>
+    <workbookView windowWidth="27660" windowHeight="13480"/>
   </bookViews>
   <sheets>
     <sheet name="Eval Results" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2537" uniqueCount="792">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2612" uniqueCount="828">
   <si>
     <t>Model</t>
   </si>
@@ -2403,6 +2403,114 @@
   </si>
   <si>
     <t>20.0/23</t>
+  </si>
+  <si>
+    <t>Kimi K2.6</t>
+  </si>
+  <si>
+    <t>https://www.kimi.com/blog/kimi-k2-6</t>
+  </si>
+  <si>
+    <t>261.58/358</t>
+  </si>
+  <si>
+    <t>32.96/43</t>
+  </si>
+  <si>
+    <t>19/26</t>
+  </si>
+  <si>
+    <t>38/47</t>
+  </si>
+  <si>
+    <t>38.63/47</t>
+  </si>
+  <si>
+    <t>17/23</t>
+  </si>
+  <si>
+    <t>51.12/93</t>
+  </si>
+  <si>
+    <t>19/24</t>
+  </si>
+  <si>
+    <t>12.87/17</t>
+  </si>
+  <si>
+    <t>21/23</t>
+  </si>
+  <si>
+    <t>OpenAPA</t>
+  </si>
+  <si>
+    <t>Laiye</t>
+  </si>
+  <si>
+    <t>282.8/361</t>
+  </si>
+  <si>
+    <t>44.0/47</t>
+  </si>
+  <si>
+    <t>38.96/47</t>
+  </si>
+  <si>
+    <t>61.14/93</t>
+  </si>
+  <si>
+    <t>20.0/24</t>
+  </si>
+  <si>
+    <t>15.75/17</t>
+  </si>
+  <si>
+    <t>Holo3-35B-A3B run1+repair</t>
+  </si>
+  <si>
+    <t>H Company</t>
+  </si>
+  <si>
+    <t>https://hcompany.ai/holo3</t>
+  </si>
+  <si>
+    <t>296.41/359</t>
+  </si>
+  <si>
+    <t>36.96/44</t>
+  </si>
+  <si>
+    <t>41.55/47</t>
+  </si>
+  <si>
+    <t>60.94/93</t>
+  </si>
+  <si>
+    <t>23.00/24</t>
+  </si>
+  <si>
+    <t>14.00/15</t>
+  </si>
+  <si>
+    <t>15.99/17</t>
+  </si>
+  <si>
+    <t>22.00/23</t>
+  </si>
+  <si>
+    <t>Holo3-35B-A3B run2</t>
+  </si>
+  <si>
+    <t>280.55/359</t>
+  </si>
+  <si>
+    <t>31.96/44</t>
+  </si>
+  <si>
+    <t>36.55/47</t>
+  </si>
+  <si>
+    <t>56.09/93</t>
   </si>
 </sst>
 </file>
@@ -3103,7 +3211,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3150,6 +3258,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -13719,29 +13830,73 @@
       <c r="AB136" s="4"/>
       <c r="AC136" s="4"/>
     </row>
-    <row r="137" ht="15.15" spans="1:29">
-      <c r="A137" s="4"/>
-      <c r="B137" s="4"/>
-      <c r="C137" s="4"/>
-      <c r="D137" s="4"/>
-      <c r="E137" s="4"/>
-      <c r="F137" s="4"/>
-      <c r="G137" s="4"/>
-      <c r="H137" s="4"/>
-      <c r="I137" s="4"/>
-      <c r="J137" s="4"/>
-      <c r="K137" s="4"/>
-      <c r="L137" s="4"/>
-      <c r="M137" s="4"/>
-      <c r="N137" s="4"/>
-      <c r="O137" s="4"/>
-      <c r="P137" s="4"/>
-      <c r="Q137" s="4"/>
-      <c r="R137" s="4"/>
-      <c r="S137" s="4"/>
-      <c r="T137" s="4"/>
-      <c r="U137" s="4"/>
-      <c r="V137" s="4"/>
+    <row r="137" spans="1:29">
+      <c r="A137" s="3" t="s">
+        <v>792</v>
+      </c>
+      <c r="B137" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>793</v>
+      </c>
+      <c r="D137" s="3" t="s">
+        <v>753</v>
+      </c>
+      <c r="E137" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F137" s="7">
+        <v>100</v>
+      </c>
+      <c r="G137" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H137" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I137" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J137" s="14">
+        <v>46132</v>
+      </c>
+      <c r="K137" s="7">
+        <v>73.06</v>
+      </c>
+      <c r="L137" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="M137" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="N137" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="O137" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="P137" s="3" t="s">
+        <v>798</v>
+      </c>
+      <c r="Q137" s="3" t="s">
+        <v>799</v>
+      </c>
+      <c r="R137" s="3" t="s">
+        <v>800</v>
+      </c>
+      <c r="S137" s="3" t="s">
+        <v>801</v>
+      </c>
+      <c r="T137" s="17">
+        <v>46371</v>
+      </c>
+      <c r="U137" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="V137" s="3" t="s">
+        <v>803</v>
+      </c>
       <c r="W137" s="4"/>
       <c r="X137" s="4"/>
       <c r="Y137" s="4"/>
@@ -13750,29 +13905,73 @@
       <c r="AB137" s="4"/>
       <c r="AC137" s="4"/>
     </row>
-    <row r="138" ht="15.15" spans="1:29">
-      <c r="A138" s="4"/>
-      <c r="B138" s="4"/>
-      <c r="C138" s="4"/>
-      <c r="D138" s="4"/>
-      <c r="E138" s="4"/>
-      <c r="F138" s="4"/>
-      <c r="G138" s="4"/>
-      <c r="H138" s="4"/>
-      <c r="I138" s="4"/>
-      <c r="J138" s="4"/>
-      <c r="K138" s="4"/>
-      <c r="L138" s="4"/>
-      <c r="M138" s="4"/>
-      <c r="N138" s="4"/>
-      <c r="O138" s="4"/>
-      <c r="P138" s="4"/>
-      <c r="Q138" s="4"/>
-      <c r="R138" s="4"/>
-      <c r="S138" s="4"/>
-      <c r="T138" s="4"/>
-      <c r="U138" s="4"/>
-      <c r="V138" s="4"/>
+    <row r="138" spans="1:29">
+      <c r="A138" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="B138" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="D138" s="3" t="s">
+        <v>805</v>
+      </c>
+      <c r="E138" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="F138" s="7">
+        <v>100</v>
+      </c>
+      <c r="G138" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H138" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I138" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J138" s="14">
+        <v>46129</v>
+      </c>
+      <c r="K138" s="7">
+        <v>78.34</v>
+      </c>
+      <c r="L138" s="3" t="s">
+        <v>806</v>
+      </c>
+      <c r="M138" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="N138" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="O138" s="3" t="s">
+        <v>807</v>
+      </c>
+      <c r="P138" s="3" t="s">
+        <v>808</v>
+      </c>
+      <c r="Q138" s="3" t="s">
+        <v>756</v>
+      </c>
+      <c r="R138" s="3" t="s">
+        <v>809</v>
+      </c>
+      <c r="S138" s="3" t="s">
+        <v>810</v>
+      </c>
+      <c r="T138" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="U138" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="V138" s="3" t="s">
+        <v>708</v>
+      </c>
       <c r="W138" s="4"/>
       <c r="X138" s="4"/>
       <c r="Y138" s="4"/>
@@ -13781,29 +13980,73 @@
       <c r="AB138" s="4"/>
       <c r="AC138" s="4"/>
     </row>
-    <row r="139" ht="15.15" spans="1:29">
-      <c r="A139" s="4"/>
-      <c r="B139" s="4"/>
-      <c r="C139" s="4"/>
-      <c r="D139" s="4"/>
-      <c r="E139" s="4"/>
-      <c r="F139" s="4"/>
-      <c r="G139" s="4"/>
-      <c r="H139" s="4"/>
-      <c r="I139" s="4"/>
-      <c r="J139" s="4"/>
-      <c r="K139" s="4"/>
-      <c r="L139" s="4"/>
-      <c r="M139" s="4"/>
-      <c r="N139" s="4"/>
-      <c r="O139" s="4"/>
-      <c r="P139" s="4"/>
-      <c r="Q139" s="4"/>
-      <c r="R139" s="4"/>
-      <c r="S139" s="4"/>
-      <c r="T139" s="4"/>
-      <c r="U139" s="4"/>
-      <c r="V139" s="4"/>
+    <row r="139" spans="1:29">
+      <c r="A139" s="3" t="s">
+        <v>812</v>
+      </c>
+      <c r="B139" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="C139" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="D139" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F139" s="7">
+        <v>100</v>
+      </c>
+      <c r="G139" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H139" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I139" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J139" s="14">
+        <v>46132</v>
+      </c>
+      <c r="K139" s="7">
+        <v>82.56</v>
+      </c>
+      <c r="L139" s="3" t="s">
+        <v>815</v>
+      </c>
+      <c r="M139" s="3" t="s">
+        <v>816</v>
+      </c>
+      <c r="N139" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="O139" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="P139" s="3" t="s">
+        <v>817</v>
+      </c>
+      <c r="Q139" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="R139" s="3" t="s">
+        <v>818</v>
+      </c>
+      <c r="S139" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="T139" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="U139" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="V139" s="3" t="s">
+        <v>822</v>
+      </c>
       <c r="W139" s="4"/>
       <c r="X139" s="4"/>
       <c r="Y139" s="4"/>
@@ -13812,29 +14055,73 @@
       <c r="AB139" s="4"/>
       <c r="AC139" s="4"/>
     </row>
-    <row r="140" ht="15.15" spans="1:29">
-      <c r="A140" s="4"/>
-      <c r="B140" s="4"/>
-      <c r="C140" s="4"/>
-      <c r="D140" s="4"/>
-      <c r="E140" s="4"/>
-      <c r="F140" s="4"/>
-      <c r="G140" s="4"/>
-      <c r="H140" s="4"/>
-      <c r="I140" s="4"/>
-      <c r="J140" s="4"/>
-      <c r="K140" s="4"/>
-      <c r="L140" s="4"/>
-      <c r="M140" s="4"/>
-      <c r="N140" s="4"/>
-      <c r="O140" s="4"/>
-      <c r="P140" s="4"/>
-      <c r="Q140" s="4"/>
-      <c r="R140" s="4"/>
-      <c r="S140" s="4"/>
-      <c r="T140" s="4"/>
-      <c r="U140" s="4"/>
-      <c r="V140" s="4"/>
+    <row r="140" spans="1:29">
+      <c r="A140" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="B140" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="C140" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="D140" s="3" t="s">
+        <v>813</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F140" s="7">
+        <v>100</v>
+      </c>
+      <c r="G140" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H140" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I140" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J140" s="14">
+        <v>46132</v>
+      </c>
+      <c r="K140" s="7">
+        <v>78.15</v>
+      </c>
+      <c r="L140" s="3" t="s">
+        <v>824</v>
+      </c>
+      <c r="M140" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="N140" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="O140" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="P140" s="3" t="s">
+        <v>826</v>
+      </c>
+      <c r="Q140" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="R140" s="3" t="s">
+        <v>827</v>
+      </c>
+      <c r="S140" s="3" t="s">
+        <v>819</v>
+      </c>
+      <c r="T140" s="3" t="s">
+        <v>820</v>
+      </c>
+      <c r="U140" s="3" t="s">
+        <v>821</v>
+      </c>
+      <c r="V140" s="3" t="s">
+        <v>822</v>
+      </c>
       <c r="W140" s="4"/>
       <c r="X140" s="4"/>
       <c r="Y140" s="4"/>
@@ -43019,6 +43306,9 @@
     <hyperlink ref="C134" r:id="rId38" display="https://github.com/wadang/muscle-mem-agent" tooltip="https://github.com/wadang/muscle-mem-agent"/>
     <hyperlink ref="C135" r:id="rId39" display="https://www.anthropic.com/news/claude-sonnet-4-6" tooltip="https://www.anthropic.com/news/claude-sonnet-4-6"/>
     <hyperlink ref="C136" r:id="rId40" display="https://arxiv.org/abs/2602.16855" tooltip="https://arxiv.org/abs/2602.16855"/>
+    <hyperlink ref="C137" r:id="rId41" display="https://www.kimi.com/blog/kimi-k2-6" tooltip="https://www.kimi.com/blog/kimi-k2-6"/>
+    <hyperlink ref="C139" r:id="rId42" display="https://hcompany.ai/holo3" tooltip="https://hcompany.ai/holo3"/>
+    <hyperlink ref="C140" r:id="rId42" display="https://hcompany.ai/holo3" tooltip="https://hcompany.ai/holo3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/static/data/osworld_verified_results.xlsx
+++ b/static/data/osworld_verified_results.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2612" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2612" uniqueCount="827">
   <si>
     <t>Model</t>
   </si>
@@ -2465,7 +2465,7 @@
     <t>15.75/17</t>
   </si>
   <si>
-    <t>Holo3-35B-A3B run1+repair</t>
+    <t>Holo3-35B-A3B</t>
   </si>
   <si>
     <t>H Company</t>
@@ -2496,9 +2496,6 @@
   </si>
   <si>
     <t>22.00/23</t>
-  </si>
-  <si>
-    <t>Holo3-35B-A3B run2</t>
   </si>
   <si>
     <t>280.55/359</t>
@@ -14057,7 +14054,7 @@
     </row>
     <row r="140" spans="1:29">
       <c r="A140" s="3" t="s">
-        <v>823</v>
+        <v>812</v>
       </c>
       <c r="B140" s="3" t="s">
         <v>813</v>
@@ -14090,10 +14087,10 @@
         <v>78.15</v>
       </c>
       <c r="L140" s="3" t="s">
+        <v>823</v>
+      </c>
+      <c r="M140" s="3" t="s">
         <v>824</v>
-      </c>
-      <c r="M140" s="3" t="s">
-        <v>825</v>
       </c>
       <c r="N140" s="3" t="s">
         <v>658</v>
@@ -14102,13 +14099,13 @@
         <v>624</v>
       </c>
       <c r="P140" s="3" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>613</v>
       </c>
       <c r="R140" s="3" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="S140" s="3" t="s">
         <v>819</v>

--- a/static/data/osworld_verified_results.xlsx
+++ b/static/data/osworld_verified_results.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2612" uniqueCount="827">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2612" uniqueCount="828">
   <si>
     <t>Model</t>
   </si>
@@ -2445,6 +2445,9 @@
   </si>
   <si>
     <t>Laiye</t>
+  </si>
+  <si>
+    <t>https: //github.com/laiye-ai/open-apa</t>
   </si>
   <si>
     <t>282.8/361</t>
@@ -13910,7 +13913,7 @@
         <v>805</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>524</v>
+        <v>806</v>
       </c>
       <c r="D138" s="3" t="s">
         <v>805</v>
@@ -13925,7 +13928,7 @@
         <v>27</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>27</v>
+        <v>429</v>
       </c>
       <c r="I138" s="3" t="s">
         <v>27</v>
@@ -13937,7 +13940,7 @@
         <v>78.34</v>
       </c>
       <c r="L138" s="3" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="M138" s="3" t="s">
         <v>590</v>
@@ -13946,25 +13949,25 @@
         <v>737</v>
       </c>
       <c r="O138" s="3" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="P138" s="3" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="Q138" s="3" t="s">
         <v>756</v>
       </c>
       <c r="R138" s="3" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="S138" s="3" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="T138" s="3" t="s">
         <v>706</v>
       </c>
       <c r="U138" s="3" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="V138" s="3" t="s">
         <v>708</v>
@@ -13979,16 +13982,16 @@
     </row>
     <row r="139" spans="1:29">
       <c r="A139" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C139" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="D139" s="3" t="s">
         <v>814</v>
-      </c>
-      <c r="D139" s="3" t="s">
-        <v>813</v>
       </c>
       <c r="E139" s="6" t="s">
         <v>26</v>
@@ -14012,10 +14015,10 @@
         <v>82.56</v>
       </c>
       <c r="L139" s="3" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="M139" s="3" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="N139" s="3" t="s">
         <v>658</v>
@@ -14024,25 +14027,25 @@
         <v>619</v>
       </c>
       <c r="P139" s="3" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="Q139" s="3" t="s">
         <v>671</v>
       </c>
       <c r="R139" s="3" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="S139" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="T139" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="U139" s="3" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="V139" s="3" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="W139" s="4"/>
       <c r="X139" s="4"/>
@@ -14054,16 +14057,16 @@
     </row>
     <row r="140" spans="1:29">
       <c r="A140" s="3" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C140" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="D140" s="3" t="s">
         <v>814</v>
-      </c>
-      <c r="D140" s="3" t="s">
-        <v>813</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>26</v>
@@ -14087,10 +14090,10 @@
         <v>78.15</v>
       </c>
       <c r="L140" s="3" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="M140" s="3" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="N140" s="3" t="s">
         <v>658</v>
@@ -14099,25 +14102,25 @@
         <v>624</v>
       </c>
       <c r="P140" s="3" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="Q140" s="3" t="s">
         <v>613</v>
       </c>
       <c r="R140" s="3" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="S140" s="3" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="T140" s="3" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="U140" s="3" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="V140" s="3" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="W140" s="4"/>
       <c r="X140" s="4"/>

--- a/static/data/osworld_verified_results.xlsx
+++ b/static/data/osworld_verified_results.xlsx
@@ -2447,7 +2447,7 @@
     <t>Laiye</t>
   </si>
   <si>
-    <t>https: //github.com/laiye-ai/open-apa</t>
+    <t>https://github.com/laiye-ai/open-apa</t>
   </si>
   <si>
     <t>282.8/361</t>
@@ -13912,7 +13912,7 @@
       <c r="B138" s="3" t="s">
         <v>805</v>
       </c>
-      <c r="C138" s="3" t="s">
+      <c r="C138" s="5" t="s">
         <v>806</v>
       </c>
       <c r="D138" s="3" t="s">
@@ -43307,8 +43307,9 @@
     <hyperlink ref="C135" r:id="rId39" display="https://www.anthropic.com/news/claude-sonnet-4-6" tooltip="https://www.anthropic.com/news/claude-sonnet-4-6"/>
     <hyperlink ref="C136" r:id="rId40" display="https://arxiv.org/abs/2602.16855" tooltip="https://arxiv.org/abs/2602.16855"/>
     <hyperlink ref="C137" r:id="rId41" display="https://www.kimi.com/blog/kimi-k2-6" tooltip="https://www.kimi.com/blog/kimi-k2-6"/>
-    <hyperlink ref="C139" r:id="rId42" display="https://hcompany.ai/holo3" tooltip="https://hcompany.ai/holo3"/>
-    <hyperlink ref="C140" r:id="rId42" display="https://hcompany.ai/holo3" tooltip="https://hcompany.ai/holo3"/>
+    <hyperlink ref="C138" r:id="rId42" display="https://github.com/laiye-ai/open-apa" tooltip="https://github.com/laiye-ai/open-apa"/>
+    <hyperlink ref="C139" r:id="rId43" display="https://hcompany.ai/holo3" tooltip="https://hcompany.ai/holo3"/>
+    <hyperlink ref="C140" r:id="rId43" display="https://hcompany.ai/holo3" tooltip="https://hcompany.ai/holo3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/static/data/osworld_verified_results.xlsx
+++ b/static/data/osworld_verified_results.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2612" uniqueCount="828">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2631" uniqueCount="837">
   <si>
     <t>Model</t>
   </si>
@@ -2303,7 +2303,7 @@
     <t>10.85/17</t>
   </si>
   <si>
-    <t>HIPPO Agent w/Opus 4.5</t>
+    <t>HIPPO Agent w/ Opus 4.5</t>
   </si>
   <si>
     <t>https://github.com/wadang/muscle-mem-agent</t>
@@ -2441,7 +2441,7 @@
     <t>21/23</t>
   </si>
   <si>
-    <t>OpenAPA</t>
+    <t>OpenAPA w/ gemini-3.1-pro</t>
   </si>
   <si>
     <t>Laiye</t>
@@ -2511,6 +2511,33 @@
   </si>
   <si>
     <t>56.09/93</t>
+  </si>
+  <si>
+    <t>VLAA-GUI w/ Opus 4.5</t>
+  </si>
+  <si>
+    <t>UCSC VLAA Lab</t>
+  </si>
+  <si>
+    <t>https://ucsc-vlaa.github.io/VLAA-GUI/</t>
+  </si>
+  <si>
+    <t>Qijun Han, Haoqin Tu, Zijun Wang</t>
+  </si>
+  <si>
+    <t>272.24/357</t>
+  </si>
+  <si>
+    <t>42.00/47</t>
+  </si>
+  <si>
+    <t>35.58/47</t>
+  </si>
+  <si>
+    <t>56.81/93</t>
+  </si>
+  <si>
+    <t>11.89/14</t>
   </si>
 </sst>
 </file>
@@ -14130,29 +14157,73 @@
       <c r="AB140" s="4"/>
       <c r="AC140" s="4"/>
     </row>
-    <row r="141" ht="15.15" spans="1:29">
-      <c r="A141" s="4"/>
-      <c r="B141" s="4"/>
-      <c r="C141" s="4"/>
-      <c r="D141" s="4"/>
-      <c r="E141" s="4"/>
-      <c r="F141" s="4"/>
-      <c r="G141" s="4"/>
-      <c r="H141" s="4"/>
-      <c r="I141" s="4"/>
-      <c r="J141" s="4"/>
-      <c r="K141" s="4"/>
-      <c r="L141" s="4"/>
-      <c r="M141" s="4"/>
-      <c r="N141" s="4"/>
-      <c r="O141" s="4"/>
-      <c r="P141" s="4"/>
-      <c r="Q141" s="4"/>
-      <c r="R141" s="4"/>
-      <c r="S141" s="4"/>
-      <c r="T141" s="4"/>
-      <c r="U141" s="4"/>
-      <c r="V141" s="4"/>
+    <row r="141" ht="44.75" spans="1:29">
+      <c r="A141" s="3" t="s">
+        <v>828</v>
+      </c>
+      <c r="B141" s="3" t="s">
+        <v>829</v>
+      </c>
+      <c r="C141" s="5" t="s">
+        <v>830</v>
+      </c>
+      <c r="D141" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="E141" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="F141" s="7">
+        <v>100</v>
+      </c>
+      <c r="G141" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H141" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="I141" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J141" s="14">
+        <v>46132</v>
+      </c>
+      <c r="K141" s="7">
+        <v>76.26</v>
+      </c>
+      <c r="L141" s="3" t="s">
+        <v>832</v>
+      </c>
+      <c r="M141" s="3" t="s">
+        <v>782</v>
+      </c>
+      <c r="N141" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="O141" s="3" t="s">
+        <v>833</v>
+      </c>
+      <c r="P141" s="3" t="s">
+        <v>834</v>
+      </c>
+      <c r="Q141" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="R141" s="3" t="s">
+        <v>835</v>
+      </c>
+      <c r="S141" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="T141" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="U141" s="3" t="s">
+        <v>836</v>
+      </c>
+      <c r="V141" s="3" t="s">
+        <v>680</v>
+      </c>
       <c r="W141" s="4"/>
       <c r="X141" s="4"/>
       <c r="Y141" s="4"/>
@@ -43310,6 +43381,7 @@
     <hyperlink ref="C138" r:id="rId42" display="https://github.com/laiye-ai/open-apa" tooltip="https://github.com/laiye-ai/open-apa"/>
     <hyperlink ref="C139" r:id="rId43" display="https://hcompany.ai/holo3" tooltip="https://hcompany.ai/holo3"/>
     <hyperlink ref="C140" r:id="rId43" display="https://hcompany.ai/holo3" tooltip="https://hcompany.ai/holo3"/>
+    <hyperlink ref="C141" r:id="rId44" display="https://ucsc-vlaa.github.io/VLAA-GUI/" tooltip="https://ucsc-vlaa.github.io/VLAA-GUI/"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/static/data/osworld_verified_results.xlsx
+++ b/static/data/osworld_verified_results.xlsx
@@ -2522,7 +2522,7 @@
     <t>https://ucsc-vlaa.github.io/VLAA-GUI/</t>
   </si>
   <si>
-    <t>Qijun Han, Haoqin Tu, Zijun Wang</t>
+    <t>VLAA Lab</t>
   </si>
   <si>
     <t>272.24/357</t>
@@ -14157,7 +14157,7 @@
       <c r="AB140" s="4"/>
       <c r="AC140" s="4"/>
     </row>
-    <row r="141" ht="44.75" spans="1:29">
+    <row r="141" spans="1:29">
       <c r="A141" s="3" t="s">
         <v>828</v>
       </c>

--- a/static/data/osworld_verified_results.xlsx
+++ b/static/data/osworld_verified_results.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="13480"/>
+    <workbookView windowWidth="27660" windowHeight="13320"/>
   </bookViews>
   <sheets>
     <sheet name="Eval Results" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2631" uniqueCount="837">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2669" uniqueCount="857">
   <si>
     <t>Model</t>
   </si>
@@ -2538,6 +2538,66 @@
   </si>
   <si>
     <t>11.89/14</t>
+  </si>
+  <si>
+    <t>Pointer Agent w/ Opus 4.7</t>
+  </si>
+  <si>
+    <t>Pointer</t>
+  </si>
+  <si>
+    <t>https://pointer.ai/blog/sota</t>
+  </si>
+  <si>
+    <t>Pointer Team</t>
+  </si>
+  <si>
+    <t>301.94 / 361</t>
+  </si>
+  <si>
+    <t>35.96/46</t>
+  </si>
+  <si>
+    <t>43.0/47</t>
+  </si>
+  <si>
+    <t>42.96/47</t>
+  </si>
+  <si>
+    <t>21.0/23</t>
+  </si>
+  <si>
+    <t>69.16/93</t>
+  </si>
+  <si>
+    <t>23.0/24</t>
+  </si>
+  <si>
+    <t>14.86/17</t>
+  </si>
+  <si>
+    <t>Pointer Agent w/ Sonnet 4.6</t>
+  </si>
+  <si>
+    <t>293.22 / 360</t>
+  </si>
+  <si>
+    <t>32.96/45</t>
+  </si>
+  <si>
+    <t>42.0/47</t>
+  </si>
+  <si>
+    <t>43.96/47</t>
+  </si>
+  <si>
+    <t>60.43/93</t>
+  </si>
+  <si>
+    <t>22.0/24</t>
+  </si>
+  <si>
+    <t>15.87/17</t>
   </si>
 </sst>
 </file>
@@ -14232,29 +14292,73 @@
       <c r="AB141" s="4"/>
       <c r="AC141" s="4"/>
     </row>
-    <row r="142" ht="15.15" spans="1:29">
-      <c r="A142" s="4"/>
-      <c r="B142" s="4"/>
-      <c r="C142" s="4"/>
-      <c r="D142" s="4"/>
-      <c r="E142" s="4"/>
-      <c r="F142" s="4"/>
-      <c r="G142" s="4"/>
-      <c r="H142" s="4"/>
-      <c r="I142" s="4"/>
-      <c r="J142" s="4"/>
-      <c r="K142" s="4"/>
-      <c r="L142" s="4"/>
-      <c r="M142" s="4"/>
-      <c r="N142" s="4"/>
-      <c r="O142" s="4"/>
-      <c r="P142" s="4"/>
-      <c r="Q142" s="4"/>
-      <c r="R142" s="4"/>
-      <c r="S142" s="4"/>
-      <c r="T142" s="4"/>
-      <c r="U142" s="4"/>
-      <c r="V142" s="4"/>
+    <row r="142" spans="1:29">
+      <c r="A142" s="3" t="s">
+        <v>837</v>
+      </c>
+      <c r="B142" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="C142" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="D142" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="E142" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="F142" s="7">
+        <v>100</v>
+      </c>
+      <c r="G142" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H142" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="I142" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J142" s="14">
+        <v>46163</v>
+      </c>
+      <c r="K142" s="7">
+        <v>83.64</v>
+      </c>
+      <c r="L142" s="3" t="s">
+        <v>841</v>
+      </c>
+      <c r="M142" s="3" t="s">
+        <v>842</v>
+      </c>
+      <c r="N142" s="3" t="s">
+        <v>725</v>
+      </c>
+      <c r="O142" s="3" t="s">
+        <v>843</v>
+      </c>
+      <c r="P142" s="3" t="s">
+        <v>844</v>
+      </c>
+      <c r="Q142" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="R142" s="3" t="s">
+        <v>846</v>
+      </c>
+      <c r="S142" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="T142" s="3" t="s">
+        <v>750</v>
+      </c>
+      <c r="U142" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="V142" s="3" t="s">
+        <v>845</v>
+      </c>
       <c r="W142" s="4"/>
       <c r="X142" s="4"/>
       <c r="Y142" s="4"/>
@@ -14263,29 +14367,73 @@
       <c r="AB142" s="4"/>
       <c r="AC142" s="4"/>
     </row>
-    <row r="143" ht="15.15" spans="1:29">
-      <c r="A143" s="4"/>
-      <c r="B143" s="4"/>
-      <c r="C143" s="4"/>
-      <c r="D143" s="4"/>
-      <c r="E143" s="4"/>
-      <c r="F143" s="4"/>
-      <c r="G143" s="4"/>
-      <c r="H143" s="4"/>
-      <c r="I143" s="4"/>
-      <c r="J143" s="4"/>
-      <c r="K143" s="4"/>
-      <c r="L143" s="4"/>
-      <c r="M143" s="4"/>
-      <c r="N143" s="4"/>
-      <c r="O143" s="4"/>
-      <c r="P143" s="4"/>
-      <c r="Q143" s="4"/>
-      <c r="R143" s="4"/>
-      <c r="S143" s="4"/>
-      <c r="T143" s="4"/>
-      <c r="U143" s="4"/>
-      <c r="V143" s="4"/>
+    <row r="143" spans="1:29">
+      <c r="A143" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="B143" s="3" t="s">
+        <v>838</v>
+      </c>
+      <c r="C143" s="5" t="s">
+        <v>839</v>
+      </c>
+      <c r="D143" s="3" t="s">
+        <v>840</v>
+      </c>
+      <c r="E143" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="F143" s="7">
+        <v>100</v>
+      </c>
+      <c r="G143" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H143" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="I143" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J143" s="14">
+        <v>46163</v>
+      </c>
+      <c r="K143" s="7">
+        <v>81.45</v>
+      </c>
+      <c r="L143" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="M143" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="N143" s="3" t="s">
+        <v>737</v>
+      </c>
+      <c r="O143" s="3" t="s">
+        <v>852</v>
+      </c>
+      <c r="P143" s="3" t="s">
+        <v>853</v>
+      </c>
+      <c r="Q143" s="3" t="s">
+        <v>845</v>
+      </c>
+      <c r="R143" s="3" t="s">
+        <v>854</v>
+      </c>
+      <c r="S143" s="3" t="s">
+        <v>855</v>
+      </c>
+      <c r="T143" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="U143" s="3" t="s">
+        <v>856</v>
+      </c>
+      <c r="V143" s="3" t="s">
+        <v>769</v>
+      </c>
       <c r="W143" s="4"/>
       <c r="X143" s="4"/>
       <c r="Y143" s="4"/>
@@ -43382,6 +43530,8 @@
     <hyperlink ref="C139" r:id="rId43" display="https://hcompany.ai/holo3" tooltip="https://hcompany.ai/holo3"/>
     <hyperlink ref="C140" r:id="rId43" display="https://hcompany.ai/holo3" tooltip="https://hcompany.ai/holo3"/>
     <hyperlink ref="C141" r:id="rId44" display="https://ucsc-vlaa.github.io/VLAA-GUI/" tooltip="https://ucsc-vlaa.github.io/VLAA-GUI/"/>
+    <hyperlink ref="C142" r:id="rId45" display="https://pointer.ai/blog/sota" tooltip="https://pointer.ai/blog/sota"/>
+    <hyperlink ref="C143" r:id="rId45" display="https://pointer.ai/blog/sota" tooltip="https://pointer.ai/blog/sota"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/static/data/osworld_verified_results.xlsx
+++ b/static/data/osworld_verified_results.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2669" uniqueCount="857">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2688" uniqueCount="867">
   <si>
     <t>Model</t>
   </si>
@@ -2546,7 +2546,7 @@
     <t>Pointer</t>
   </si>
   <si>
-    <t>https://pointer.ai/blog/sota</t>
+    <t>https://pointer.ai/blog/sota?utm_source=osworld&amp;utm_medium=leaderboard&amp;utm_campaign=sota</t>
   </si>
   <si>
     <t>Pointer Team</t>
@@ -2598,6 +2598,36 @@
   </si>
   <si>
     <t>15.87/17</t>
+  </si>
+  <si>
+    <t>Qwen 3.7 Plus</t>
+  </si>
+  <si>
+    <t>https://qwen.ai/blog?id=qwen3.7</t>
+  </si>
+  <si>
+    <t>264 / 360</t>
+  </si>
+  <si>
+    <t>32.0/45</t>
+  </si>
+  <si>
+    <t>17.0/26</t>
+  </si>
+  <si>
+    <t>37.0/47</t>
+  </si>
+  <si>
+    <t>40.0/47</t>
+  </si>
+  <si>
+    <t>55.1/93</t>
+  </si>
+  <si>
+    <t>19.0/24</t>
+  </si>
+  <si>
+    <t>14.0/17</t>
   </si>
 </sst>
 </file>
@@ -14292,7 +14322,7 @@
       <c r="AB141" s="4"/>
       <c r="AC141" s="4"/>
     </row>
-    <row r="142" spans="1:29">
+    <row r="142" ht="29.75" spans="1:29">
       <c r="A142" s="3" t="s">
         <v>837</v>
       </c>
@@ -14367,7 +14397,7 @@
       <c r="AB142" s="4"/>
       <c r="AC142" s="4"/>
     </row>
-    <row r="143" spans="1:29">
+    <row r="143" ht="29.75" spans="1:29">
       <c r="A143" s="3" t="s">
         <v>849</v>
       </c>
@@ -14442,29 +14472,73 @@
       <c r="AB143" s="4"/>
       <c r="AC143" s="4"/>
     </row>
-    <row r="144" ht="15.15" spans="1:29">
-      <c r="A144" s="4"/>
-      <c r="B144" s="4"/>
-      <c r="C144" s="4"/>
-      <c r="D144" s="4"/>
-      <c r="E144" s="4"/>
-      <c r="F144" s="4"/>
-      <c r="G144" s="4"/>
-      <c r="H144" s="4"/>
-      <c r="I144" s="4"/>
-      <c r="J144" s="4"/>
-      <c r="K144" s="4"/>
-      <c r="L144" s="4"/>
-      <c r="M144" s="4"/>
-      <c r="N144" s="4"/>
-      <c r="O144" s="4"/>
-      <c r="P144" s="4"/>
-      <c r="Q144" s="4"/>
-      <c r="R144" s="4"/>
-      <c r="S144" s="4"/>
-      <c r="T144" s="4"/>
-      <c r="U144" s="4"/>
-      <c r="V144" s="4"/>
+    <row r="144" ht="29.75" spans="1:29">
+      <c r="A144" s="3" t="s">
+        <v>857</v>
+      </c>
+      <c r="B144" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="C144" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="D144" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="E144" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F144" s="7">
+        <v>100</v>
+      </c>
+      <c r="G144" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H144" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I144" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J144" s="14">
+        <v>46167</v>
+      </c>
+      <c r="K144" s="7">
+        <v>73.3</v>
+      </c>
+      <c r="L144" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="M144" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="N144" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="O144" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="P144" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="Q144" s="3" t="s">
+        <v>791</v>
+      </c>
+      <c r="R144" s="3" t="s">
+        <v>864</v>
+      </c>
+      <c r="S144" s="3" t="s">
+        <v>865</v>
+      </c>
+      <c r="T144" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="U144" s="3" t="s">
+        <v>866</v>
+      </c>
+      <c r="V144" s="3" t="s">
+        <v>708</v>
+      </c>
       <c r="W144" s="4"/>
       <c r="X144" s="4"/>
       <c r="Y144" s="4"/>
@@ -43530,8 +43604,9 @@
     <hyperlink ref="C139" r:id="rId43" display="https://hcompany.ai/holo3" tooltip="https://hcompany.ai/holo3"/>
     <hyperlink ref="C140" r:id="rId43" display="https://hcompany.ai/holo3" tooltip="https://hcompany.ai/holo3"/>
     <hyperlink ref="C141" r:id="rId44" display="https://ucsc-vlaa.github.io/VLAA-GUI/" tooltip="https://ucsc-vlaa.github.io/VLAA-GUI/"/>
-    <hyperlink ref="C142" r:id="rId45" display="https://pointer.ai/blog/sota" tooltip="https://pointer.ai/blog/sota"/>
-    <hyperlink ref="C143" r:id="rId45" display="https://pointer.ai/blog/sota" tooltip="https://pointer.ai/blog/sota"/>
+    <hyperlink ref="C142" r:id="rId45" display="https://pointer.ai/blog/sota?utm_source=osworld&amp;utm_medium=leaderboard&amp;utm_campaign=sota" tooltip="https://pointer.ai/blog/sota?utm_source=osworld&amp;utm_medium=leaderboard&amp;utm_campaign=sota"/>
+    <hyperlink ref="C143" r:id="rId45" display="https://pointer.ai/blog/sota?utm_source=osworld&amp;utm_medium=leaderboard&amp;utm_campaign=sota" tooltip="https://pointer.ai/blog/sota?utm_source=osworld&amp;utm_medium=leaderboard&amp;utm_campaign=sota"/>
+    <hyperlink ref="C144" r:id="rId46" display="https://qwen.ai/blog?id=qwen3.7" tooltip="https://qwen.ai/blog?id=qwen3.7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/static/data/osworld_verified_results.xlsx
+++ b/static/data/osworld_verified_results.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="13320"/>
+    <workbookView windowWidth="27660" windowHeight="13280"/>
   </bookViews>
   <sheets>
     <sheet name="Eval Results" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2688" uniqueCount="867">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2707" uniqueCount="878">
   <si>
     <t>Model</t>
   </si>
@@ -2628,6 +2628,39 @@
   </si>
   <si>
     <t>14.0/17</t>
+  </si>
+  <si>
+    <t>MiniMax M3</t>
+  </si>
+  <si>
+    <t>MiniMax</t>
+  </si>
+  <si>
+    <t>https://www.minimaxi.com/blog/minimax-m3</t>
+  </si>
+  <si>
+    <t>MiniMax Team</t>
+  </si>
+  <si>
+    <t>269.18 / 358</t>
+  </si>
+  <si>
+    <t>34.96/46</t>
+  </si>
+  <si>
+    <t>38.0/47</t>
+  </si>
+  <si>
+    <t>34.63/47</t>
+  </si>
+  <si>
+    <t>20.97/23</t>
+  </si>
+  <si>
+    <t>56.64/92</t>
+  </si>
+  <si>
+    <t>12.99/15</t>
   </si>
 </sst>
 </file>
@@ -14547,29 +14580,73 @@
       <c r="AB144" s="4"/>
       <c r="AC144" s="4"/>
     </row>
-    <row r="145" ht="15.15" spans="1:29">
-      <c r="A145" s="4"/>
-      <c r="B145" s="4"/>
-      <c r="C145" s="4"/>
-      <c r="D145" s="4"/>
-      <c r="E145" s="4"/>
-      <c r="F145" s="4"/>
-      <c r="G145" s="4"/>
-      <c r="H145" s="4"/>
-      <c r="I145" s="4"/>
-      <c r="J145" s="4"/>
-      <c r="K145" s="4"/>
-      <c r="L145" s="4"/>
-      <c r="M145" s="4"/>
-      <c r="N145" s="4"/>
-      <c r="O145" s="4"/>
-      <c r="P145" s="4"/>
-      <c r="Q145" s="4"/>
-      <c r="R145" s="4"/>
-      <c r="S145" s="4"/>
-      <c r="T145" s="4"/>
-      <c r="U145" s="4"/>
-      <c r="V145" s="4"/>
+    <row r="145" spans="1:29">
+      <c r="A145" s="3" t="s">
+        <v>867</v>
+      </c>
+      <c r="B145" s="3" t="s">
+        <v>868</v>
+      </c>
+      <c r="C145" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="D145" s="3" t="s">
+        <v>870</v>
+      </c>
+      <c r="E145" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F145" s="7">
+        <v>100</v>
+      </c>
+      <c r="G145" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H145" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I145" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J145" s="14">
+        <v>46181</v>
+      </c>
+      <c r="K145" s="7">
+        <v>75.19</v>
+      </c>
+      <c r="L145" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="M145" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="N145" s="3" t="s">
+        <v>783</v>
+      </c>
+      <c r="O145" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="P145" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="Q145" s="3" t="s">
+        <v>875</v>
+      </c>
+      <c r="R145" s="3" t="s">
+        <v>876</v>
+      </c>
+      <c r="S145" s="3" t="s">
+        <v>811</v>
+      </c>
+      <c r="T145" s="3" t="s">
+        <v>789</v>
+      </c>
+      <c r="U145" s="3" t="s">
+        <v>877</v>
+      </c>
+      <c r="V145" s="3" t="s">
+        <v>699</v>
+      </c>
       <c r="W145" s="4"/>
       <c r="X145" s="4"/>
       <c r="Y145" s="4"/>
@@ -43607,6 +43684,7 @@
     <hyperlink ref="C142" r:id="rId45" display="https://pointer.ai/blog/sota?utm_source=osworld&amp;utm_medium=leaderboard&amp;utm_campaign=sota" tooltip="https://pointer.ai/blog/sota?utm_source=osworld&amp;utm_medium=leaderboard&amp;utm_campaign=sota"/>
     <hyperlink ref="C143" r:id="rId45" display="https://pointer.ai/blog/sota?utm_source=osworld&amp;utm_medium=leaderboard&amp;utm_campaign=sota" tooltip="https://pointer.ai/blog/sota?utm_source=osworld&amp;utm_medium=leaderboard&amp;utm_campaign=sota"/>
     <hyperlink ref="C144" r:id="rId46" display="https://qwen.ai/blog?id=qwen3.7" tooltip="https://qwen.ai/blog?id=qwen3.7"/>
+    <hyperlink ref="C145" r:id="rId47" display="https://www.minimaxi.com/blog/minimax-m3" tooltip="https://www.minimaxi.com/blog/minimax-m3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/static/data/osworld_verified_results.xlsx
+++ b/static/data/osworld_verified_results.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27660" windowHeight="13280"/>
+    <workbookView windowWidth="27660" windowHeight="13320"/>
   </bookViews>
   <sheets>
     <sheet name="Eval Results" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2707" uniqueCount="878">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2726" uniqueCount="887">
   <si>
     <t>Model</t>
   </si>
@@ -2661,6 +2661,33 @@
   </si>
   <si>
     <t>12.99/15</t>
+  </si>
+  <si>
+    <t>Coasty CUA v1</t>
+  </si>
+  <si>
+    <t>Coasty Team</t>
+  </si>
+  <si>
+    <t>https://coasty.ai</t>
+  </si>
+  <si>
+    <t>297.29 / 359</t>
+  </si>
+  <si>
+    <t>25.00/26</t>
+  </si>
+  <si>
+    <t>44.96/47</t>
+  </si>
+  <si>
+    <t>64.39/93</t>
+  </si>
+  <si>
+    <t>24.00/24</t>
+  </si>
+  <si>
+    <t>11.99/15</t>
   </si>
 </sst>
 </file>
@@ -14655,29 +14682,73 @@
       <c r="AB145" s="4"/>
       <c r="AC145" s="4"/>
     </row>
-    <row r="146" ht="15.15" spans="1:29">
-      <c r="A146" s="4"/>
-      <c r="B146" s="4"/>
-      <c r="C146" s="4"/>
-      <c r="D146" s="4"/>
-      <c r="E146" s="4"/>
-      <c r="F146" s="4"/>
-      <c r="G146" s="4"/>
-      <c r="H146" s="4"/>
-      <c r="I146" s="4"/>
-      <c r="J146" s="4"/>
-      <c r="K146" s="4"/>
-      <c r="L146" s="4"/>
-      <c r="M146" s="4"/>
-      <c r="N146" s="4"/>
-      <c r="O146" s="4"/>
-      <c r="P146" s="4"/>
-      <c r="Q146" s="4"/>
-      <c r="R146" s="4"/>
-      <c r="S146" s="4"/>
-      <c r="T146" s="4"/>
-      <c r="U146" s="4"/>
-      <c r="V146" s="4"/>
+    <row r="146" spans="1:29">
+      <c r="A146" s="15" t="s">
+        <v>878</v>
+      </c>
+      <c r="B146" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="C146" s="5" t="s">
+        <v>880</v>
+      </c>
+      <c r="D146" s="3" t="s">
+        <v>879</v>
+      </c>
+      <c r="E146" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F146" s="7">
+        <v>100</v>
+      </c>
+      <c r="G146" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="H146" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="I146" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="J146" s="14">
+        <v>46204</v>
+      </c>
+      <c r="K146" s="7">
+        <v>82.81</v>
+      </c>
+      <c r="L146" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="M146" s="15" t="s">
+        <v>618</v>
+      </c>
+      <c r="N146" s="15" t="s">
+        <v>882</v>
+      </c>
+      <c r="O146" s="15" t="s">
+        <v>833</v>
+      </c>
+      <c r="P146" s="15" t="s">
+        <v>883</v>
+      </c>
+      <c r="Q146" s="15" t="s">
+        <v>452</v>
+      </c>
+      <c r="R146" s="15" t="s">
+        <v>884</v>
+      </c>
+      <c r="S146" s="15" t="s">
+        <v>885</v>
+      </c>
+      <c r="T146" s="15" t="s">
+        <v>821</v>
+      </c>
+      <c r="U146" s="15" t="s">
+        <v>886</v>
+      </c>
+      <c r="V146" s="15" t="s">
+        <v>823</v>
+      </c>
       <c r="W146" s="4"/>
       <c r="X146" s="4"/>
       <c r="Y146" s="4"/>
@@ -43685,6 +43756,7 @@
     <hyperlink ref="C143" r:id="rId45" display="https://pointer.ai/blog/sota?utm_source=osworld&amp;utm_medium=leaderboard&amp;utm_campaign=sota" tooltip="https://pointer.ai/blog/sota?utm_source=osworld&amp;utm_medium=leaderboard&amp;utm_campaign=sota"/>
     <hyperlink ref="C144" r:id="rId46" display="https://qwen.ai/blog?id=qwen3.7" tooltip="https://qwen.ai/blog?id=qwen3.7"/>
     <hyperlink ref="C145" r:id="rId47" display="https://www.minimaxi.com/blog/minimax-m3" tooltip="https://www.minimaxi.com/blog/minimax-m3"/>
+    <hyperlink ref="C146" r:id="rId48" display="https://coasty.ai" tooltip="https://coasty.ai"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
